--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332042</v>
       </c>
       <c r="B2" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129332087</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129332025</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332042</v>
       </c>
       <c r="B2" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129332087</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129332025</v>
       </c>
       <c r="B7" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129332042</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129332087</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129332025</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>129332133</v>
       </c>
       <c r="B4" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129331992</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>129331733</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49412-2025 artfynd.xlsx
+++ b/artfynd/A 49412-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129332042</v>
+        <v>129331698</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 49412, Kulltorp, Skedshult, Sm</t>
+          <t>Kulltorp, Skedshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586638</v>
+        <v>586694</v>
       </c>
       <c r="R2" t="n">
-        <v>6439119</v>
+        <v>6439040</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,6 +761,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129332087</v>
+        <v>129332133</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,31 +791,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586653</v>
+        <v>586656</v>
       </c>
       <c r="R3" t="n">
-        <v>6439091</v>
+        <v>6439062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,17 +860,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,41 +885,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129332133</v>
+        <v>129332087</v>
       </c>
       <c r="B4" t="n">
-        <v>92913</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586656</v>
+        <v>586653</v>
       </c>
       <c r="R4" t="n">
-        <v>6439062</v>
+        <v>6439091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,13 +966,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,46 +995,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129331992</v>
+        <v>129332042</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586661</v>
+        <v>586638</v>
       </c>
       <c r="R5" t="n">
-        <v>6439098</v>
+        <v>6439119</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1082,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,46 +1100,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129331733</v>
+        <v>129332025</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586667</v>
+        <v>586638</v>
       </c>
       <c r="R6" t="n">
-        <v>6439062</v>
+        <v>6439119</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1191,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,46 +1209,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129332025</v>
+        <v>129331733</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,13 +1256,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586638</v>
+        <v>586667</v>
       </c>
       <c r="R7" t="n">
-        <v>6439119</v>
+        <v>6439062</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,6 +1316,116 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129331992</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 49412, Kulltorp, Skedshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>586661</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6439098</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
